--- a/output/2.xlsx
+++ b/output/2.xlsx
@@ -1107,30 +1107,72 @@
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>17000240</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>SLIN-静电计支撑块-ODBC</t>
+        </is>
+      </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>17000060</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>ODBC定制线</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="I6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>17000050</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>垃圾桶</t>
+        </is>
+      </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="n"/>
     </row>
     <row r="8">
